--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484540_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484540_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0591</v>
+        <v>2.608</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1069</v>
+        <v>2.9531</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0478</v>
+        <v>-0.3451</v>
       </c>
       <c r="G2" t="n">
         <v>2.2415</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3674</v>
+        <v>0.9163</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5913</v>
+        <v>0.4374</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7761</v>
+        <v>0.4789</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8035</v>
+        <v>1.2872</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4589</v>
+        <v>0.8435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3446</v>
+        <v>0.4437</v>
       </c>
       <c r="G3" t="n">
         <v>0.4183</v>
@@ -688,13 +688,13 @@
         <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2092</v>
+        <v>0.2745</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2021</v>
+        <v>0.1825</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0071</v>
+        <v>0.092</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3219</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1068</v>
+        <v>0.3202</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1165</v>
+        <v>0.2647</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2233</v>
+        <v>0.0555</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08550000000000001</v>
+        <v>-1.1763</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8776</v>
+        <v>-0.1697</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7921</v>
+        <v>-1.0065</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8932</v>
+        <v>-0.8677</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8515</v>
+        <v>0.9721</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0417</v>
+        <v>-1.8397</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8077</v>
+        <v>-0.3086</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9739</v>
+        <v>-1.1418</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8338</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.2828</v>
+        <v>1.2828</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1455</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2949</v>
+        <v>-0.1346</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4403</v>
+        <v>0.0471</v>
       </c>
       <c r="V6" t="n">
-        <v>0.945</v>
+        <v>0.3011</v>
       </c>
       <c r="W6" t="n">
         <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3219</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3663</v>
+        <v>-0.4259</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0187</v>
+        <v>0.0203</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.385</v>
+        <v>-0.4462</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3044</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3435</v>
+        <v>0.8776</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6479</v>
+        <v>-0.7921</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4637</v>
+        <v>1.8932</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6624</v>
+        <v>1.8515</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1987</v>
+        <v>0.0417</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.768</v>
+        <v>-1.8077</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3189</v>
+        <v>-0.9739</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4492</v>
+        <v>-0.8338</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0158</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7314000000000001</v>
+        <v>-0.1736</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3643</v>
+        <v>-0.391</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3672</v>
+        <v>0.2174</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2224</v>
+        <v>0.945</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8559</v>
+        <v>1.267</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6997</v>
+        <v>-0.9739</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4084</v>
+        <v>-0.3659</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2913</v>
+        <v>-0.608</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1763</v>
+        <v>-1.3044</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1697</v>
+        <v>0.3435</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0065</v>
+        <v>-1.6479</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8677</v>
+        <v>0.4637</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9721</v>
+        <v>1.6624</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8397</v>
+        <v>-1.1987</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3086</v>
+        <v>-1.768</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1418</v>
+        <v>-1.3189</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.4492</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2828</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1074</v>
+        <v>0.1239</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8077</v>
+        <v>-0.0203</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2997</v>
+        <v>0.1442</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3011</v>
+        <v>2.2224</v>
       </c>
       <c r="W8" t="n">
-        <v>1.267</v>
+        <v>2.8559</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9658</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0697</v>
+        <v>-1.6219</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9761</v>
+        <v>0.3992</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0458</v>
+        <v>-2.021</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9733</v>
@@ -1156,13 +1156,13 @@
         <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7857</v>
+        <v>0.2336</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9517</v>
+        <v>0.3748</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.166</v>
+        <v>-0.1412</v>
       </c>
       <c r="V9" t="n">
         <v>0.3011</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6197</v>
+        <v>-1.7683</v>
       </c>
       <c r="E10" t="n">
         <v>-1.8367</v>
       </c>
       <c r="F10" t="n">
-        <v>0.217</v>
+        <v>0.0684</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7589</v>
@@ -1234,13 +1234,13 @@
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3225</v>
+        <v>0.1738</v>
       </c>
       <c r="T10" t="n">
         <v>0.1456</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1769</v>
+        <v>0.0283</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9499</v>
+        <v>-3.3918</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4862</v>
+        <v>-3.1016</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4637</v>
+        <v>-0.2903</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3031</v>
@@ -1312,13 +1312,13 @@
         <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3248</v>
+        <v>0.2332</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.497</v>
+        <v>-0.1123</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1722</v>
+        <v>0.3456</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5889</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0024</v>
+        <v>-3.7168</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6586</v>
+        <v>-2.274</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3438</v>
+        <v>-1.4429</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5886</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2305</v>
+        <v>0.0551</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3854</v>
+        <v>-0.0007</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1549</v>
+        <v>0.0558</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8384</v>
+        <v>-5.5906</v>
       </c>
       <c r="E13" t="n">
         <v>-4.081</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7573</v>
+        <v>-1.5096</v>
       </c>
       <c r="G13" t="n">
         <v>-4.8301</v>
@@ -1468,13 +1468,13 @@
         <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4585</v>
+        <v>-0.2108</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0196</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4389</v>
+        <v>-0.1912</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.0931</v>
+        <v>-6.6094</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.0019</v>
+        <v>-3.6173</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0912</v>
+        <v>-2.9921</v>
       </c>
       <c r="G14" t="n">
         <v>-1.4813</v>
@@ -1546,13 +1546,13 @@
         <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7401</v>
+        <v>-0.2564</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4955</v>
+        <v>-0.1108</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2447</v>
+        <v>-0.1456</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8559</v>
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.2332</v>
+        <v>-19.233</v>
       </c>
       <c r="E15" t="n">
         <v>-10.1455</v>
@@ -1624,19 +1624,19 @@
         <v>13.7443</v>
       </c>
       <c r="S15" t="n">
-        <v>1.282</v>
+        <v>1.2821</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3507</v>
+        <v>0.351</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9312000000000001</v>
+        <v>0.9313</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9971000000000003</v>
       </c>
       <c r="W15" t="n">
-        <v>7.300699999999999</v>
+        <v>7.3007</v>
       </c>
       <c r="X15" t="n">
         <v>-8.297599999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.720700000000001</v>
+        <v>7.9806</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4372</v>
+        <v>6.668</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2835</v>
+        <v>1.3126</v>
       </c>
       <c r="G16" t="n">
         <v>1.5381</v>
@@ -1702,13 +1702,13 @@
         <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0335</v>
+        <v>0.2934</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8771</v>
+        <v>0.1079</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1564</v>
+        <v>0.1855</v>
       </c>
       <c r="V16" t="n">
         <v>4.1333</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5067</v>
+        <v>4.1854</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2814</v>
+        <v>0.9353</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2253</v>
+        <v>3.2501</v>
       </c>
       <c r="G17" t="n">
         <v>2.0904</v>
@@ -1780,13 +1780,13 @@
         <v>2.9321</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3717</v>
+        <v>0.0503</v>
       </c>
       <c r="T17" t="n">
-        <v>1.408</v>
+        <v>0.0619</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0363</v>
+        <v>-0.0115</v>
       </c>
       <c r="V17" t="n">
         <v>0.945</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8124</v>
+        <v>3.6433</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5275</v>
+        <v>3.3497</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2849</v>
+        <v>0.2936</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0253</v>
+        <v>3.7168</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2204</v>
+        <v>-0.457</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8049</v>
+        <v>4.1738</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2041</v>
+        <v>3.9824</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1363</v>
+        <v>0.065</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0678</v>
+        <v>3.9174</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1787</v>
+        <v>-0.2656</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.522</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7371</v>
+        <v>0.2564</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5498</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3814</v>
+        <v>0.1097</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2006</v>
+        <v>0.2836</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1808</v>
+        <v>-0.1738</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.786</v>
+        <v>3.4219</v>
       </c>
       <c r="E19" t="n">
-        <v>3.542</v>
+        <v>2.3352</v>
       </c>
       <c r="F19" t="n">
-        <v>0.244</v>
+        <v>1.0867</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7168</v>
+        <v>3.0253</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.457</v>
+        <v>0.2204</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1738</v>
+        <v>2.8049</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9824</v>
+        <v>3.2041</v>
       </c>
       <c r="K19" t="n">
-        <v>0.065</v>
+        <v>1.1363</v>
       </c>
       <c r="L19" t="n">
-        <v>3.9174</v>
+        <v>2.0678</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2656</v>
+        <v>-0.1787</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.522</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2564</v>
+        <v>0.7371</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1833</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2525</v>
+        <v>-0.0091</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4759</v>
+        <v>0.0083</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2234</v>
+        <v>-0.0174</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1507</v>
+        <v>2.8019</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3972</v>
+        <v>0.9741</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7534</v>
+        <v>1.8278</v>
       </c>
       <c r="G20" t="n">
         <v>3.4466</v>
@@ -2014,13 +2014,13 @@
         <v>2.1991</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0681</v>
+        <v>-0.4169</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.1938</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2974</v>
+        <v>-0.2231</v>
       </c>
       <c r="V20" t="n">
         <v>0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0912</v>
+        <v>2.6652</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5439000000000001</v>
+        <v>0.1292</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6351</v>
+        <v>2.536</v>
       </c>
       <c r="G21" t="n">
         <v>1.1852</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1935</v>
+        <v>0.3805</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7157</v>
+        <v>-0.0426</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5222</v>
+        <v>0.4231</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>P. VILLAGRASA TORTAJADA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2559</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3218</v>
+        <v>-1.252</v>
       </c>
       <c r="F22" t="n">
-        <v>2.066</v>
+        <v>1.164</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1528</v>
+        <v>0.8739</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.748</v>
+        <v>-0.5907</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9008</v>
+        <v>1.4647</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2266</v>
+        <v>1.9931</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4243</v>
+        <v>1.2013</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6509</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9262</v>
+        <v>-1.1192</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3237</v>
+        <v>-1.792</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2499</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0995</v>
+        <v>-2.7489</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>2.5656</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0134</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8258</v>
+        <v>-0.4962</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8123</v>
+        <v>-0.2824</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5785</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. VILLAGRASA TORTAJADA</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5513</v>
+        <v>-0.1685</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6366</v>
+        <v>-1.9372</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0853</v>
+        <v>1.7687</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8739</v>
+        <v>1.1528</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5907</v>
+        <v>-0.748</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4647</v>
+        <v>1.9008</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9931</v>
+        <v>0.2266</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2013</v>
+        <v>-0.4243</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.6509</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1192</v>
+        <v>0.9262</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.792</v>
+        <v>-0.3237</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6729000000000001</v>
+        <v>1.2499</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>-1.0995</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5656</v>
+        <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2419</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8808</v>
+        <v>-0.4412</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3611</v>
+        <v>0.5151</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.5785</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7788</v>
+        <v>-0.7764</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0529</v>
+        <v>-2.4759</v>
       </c>
       <c r="F24" t="n">
-        <v>1.274</v>
+        <v>1.6995</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7567</v>
@@ -2326,13 +2326,13 @@
         <v>2.0158</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2317</v>
+        <v>-0.2293</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9359</v>
+        <v>-0.359</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2958</v>
+        <v>0.1297</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6231</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9553</v>
+        <v>-1.1976</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3046</v>
+        <v>-0.8238</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.3739</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5776</v>
@@ -2404,13 +2404,13 @@
         <v>1.8326</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8541</v>
+        <v>-0.0965</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7157</v>
+        <v>-0.2349</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1385</v>
+        <v>0.1384</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2566</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.2935</v>
+        <v>-2.5936</v>
       </c>
       <c r="E26" t="n">
-        <v>1.762</v>
+        <v>1.185</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.0554</v>
+        <v>-3.7786</v>
       </c>
       <c r="G26" t="n">
         <v>-0.6746</v>
@@ -2482,13 +2482,13 @@
         <v>0.9163</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2816</v>
+        <v>-0.0185</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9517</v>
+        <v>0.3748</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6701</v>
+        <v>-0.3933</v>
       </c>
       <c r="V26" t="n">
         <v>-1.9005</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19.2329</v>
+        <v>19.8742</v>
       </c>
       <c r="E27" t="n">
-        <v>9.087499999999999</v>
+        <v>9.087599999999998</v>
       </c>
       <c r="F27" t="n">
-        <v>10.1454</v>
+        <v>10.7865</v>
       </c>
       <c r="G27" t="n">
         <v>14.0202</v>
@@ -2560,13 +2560,13 @@
         <v>19.242</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.282</v>
+        <v>-0.6412</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9313000000000002</v>
+        <v>-0.9312</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3509</v>
+        <v>0.2903</v>
       </c>
       <c r="V27" t="n">
         <v>0.996900000000001</v>
